--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -4390,7 +4390,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 35.3, "op_wape_pct": 65.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 112.0, "rev_act": 161.96, "op_pred": 12.97, "op_act": 25.93}, {"q": "2025Q4", "rev_pred": 123.37, "rev_act": 184.1, "op_pred": 14.28, "op_act": 28.23}, {"q": "2026Q1", "rev_pred": 131.11, "rev_act": 223.81, "op_pred": 15.18, "op_act": 62.05}, {"q": "2026Q2", "rev_pred": 154.99, "rev_act": 236.45, "op_pred": 17.94, "op_act": 56.03}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 35.3, "op_wape_pct": 65.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 112.0, "rev_act": 161.96, "op_pred": 12.97, "op_act": 25.93}, {"q": "2025Q4", "rev_pred": 123.37, "rev_act": 184.1, "op_pred": 14.28, "op_act": 28.23}, {"q": "2026Q1", "rev_pred": 131.11, "rev_act": 223.81, "op_pred": 15.18, "op_act": 62.05}, {"q": "2026Q2", "rev_pred": 154.99, "rev_act": 236.45, "op_pred": 17.94, "op_act": 56.03}]}</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AE$1</definedName>
@@ -4414,7 +4414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5117,35 +5117,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -5206,35 +5206,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -5384,35 +5384,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -5473,35 +5473,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5651,35 +5651,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5740,35 +5740,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5847,7 +5847,7 @@
         <v>13730</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>14360</v>
+        <v>15030</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5912,7 +5912,7 @@
         <v>15830</v>
       </c>
       <c r="T16" s="20" t="n">
-        <v>14560</v>
+        <v>15320</v>
       </c>
       <c r="U16" s="11" t="n"/>
       <c r="V16" s="10" t="n"/>
@@ -6042,7 +6042,7 @@
         <v>11494.2</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>14220</v>
+        <v>14490</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>14360</v>
+        <v>15030</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.08233129545388693</v>
+        <v>0.08233129545388691</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26446,7 +26446,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.79</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="32">
@@ -26456,7 +26456,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="33">
@@ -26496,7 +26496,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.7</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -4414,7 +4414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5117,35 +5117,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -5206,35 +5206,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -5384,35 +5384,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -5473,35 +5473,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5651,35 +5651,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5740,35 +5740,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5847,7 +5847,7 @@
         <v>13730</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>15030</v>
+        <v>14370</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -6042,7 +6042,7 @@
         <v>11494.2</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>14490</v>
+        <v>14470</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -8297,11 +8297,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>15030</v>
+        <v>14370</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,320원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26446,7 +26446,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.52</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="32">
@@ -26456,7 +26456,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="33">
@@ -26496,7 +26496,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.31</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -4414,7 +4414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -5117,35 +5117,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -5206,35 +5206,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -5384,35 +5384,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -5473,35 +5473,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5651,35 +5651,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5740,35 +5740,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5847,7 +5847,7 @@
         <v>13730</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>14370</v>
+        <v>14050</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -6042,7 +6042,7 @@
         <v>11494.2</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>14470</v>
+        <v>14342</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -8297,11 +8297,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>14370</v>
+        <v>14050</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,320원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,020원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26446,7 +26446,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.8</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="32">
@@ -26456,7 +26456,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="33">
@@ -26496,7 +26496,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.71</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AE$1</definedName>
@@ -4414,7 +4414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.08233129545388691</v>
+        <v>0.08233129545388693</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AE$1</definedName>
@@ -5117,35 +5117,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -5206,35 +5206,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -5384,35 +5384,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -5473,35 +5473,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5651,35 +5651,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5740,35 +5740,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5847,7 +5847,7 @@
         <v>13730</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>14050</v>
+        <v>14060</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -6042,7 +6042,7 @@
         <v>11494.2</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>14342</v>
+        <v>14344</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -8297,11 +8297,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>14050</v>
+        <v>14060</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,020원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,300원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.08233129545388693</v>
+        <v>0.08233129545388691</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.44</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="32">
@@ -26496,7 +26496,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.42</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -4414,7 +4414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5117,35 +5117,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -5206,35 +5206,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -5384,35 +5384,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -5473,35 +5473,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5651,35 +5651,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5740,35 +5740,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -4414,7 +4414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -4414,7 +4414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
         <v>13730</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>14060</v>
+        <v>13250</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5977,7 +5977,7 @@
         <v>8610</v>
       </c>
       <c r="T17" s="20" t="n">
-        <v>13240</v>
+        <v>12770</v>
       </c>
       <c r="U17" s="11" t="n"/>
       <c r="V17" s="10" t="n"/>
@@ -6042,7 +6042,7 @@
         <v>11494.2</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>14344</v>
+        <v>14161.7</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>14060</v>
+        <v>13250</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26446,7 +26446,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.46</v>
+        <v>14.57</v>
       </c>
     </row>
     <row r="32">
@@ -26456,7 +26456,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="33">
@@ -26496,7 +26496,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.43</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -4414,7 +4414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5117,35 +5117,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -5206,35 +5206,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -5384,35 +5384,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -5473,35 +5473,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5651,35 +5651,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5740,35 +5740,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5847,7 +5847,7 @@
         <v>13730</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>13250</v>
+        <v>12590</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5977,7 +5977,7 @@
         <v>8610</v>
       </c>
       <c r="T17" s="20" t="n">
-        <v>12770</v>
+        <v>12160</v>
       </c>
       <c r="U17" s="11" t="n"/>
       <c r="V17" s="10" t="n"/>
@@ -6042,7 +6042,7 @@
         <v>11494.2</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>14161.7</v>
+        <v>13910</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -8297,11 +8297,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>13250</v>
+        <v>12590</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,300원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,050원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26446,7 +26446,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.57</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="32">
@@ -26456,7 +26456,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="33">
@@ -26496,7 +26496,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.69</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -4414,7 +4414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5117,35 +5117,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -5206,35 +5206,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -5384,35 +5384,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -5473,35 +5473,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5651,35 +5651,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5740,35 +5740,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5847,7 +5847,7 @@
         <v>13730</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>12590</v>
+        <v>15930</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5912,7 +5912,7 @@
         <v>15830</v>
       </c>
       <c r="T16" s="20" t="n">
-        <v>15320</v>
+        <v>16200</v>
       </c>
       <c r="U16" s="11" t="n"/>
       <c r="V16" s="10" t="n"/>
@@ -6042,7 +6042,7 @@
         <v>11494.2</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>13910</v>
+        <v>14152.5</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -8297,11 +8297,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>12590</v>
+        <v>15930</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,050원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,270원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26446,7 +26446,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.84</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="32">
@@ -26456,7 +26456,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.58</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="33">
@@ -26496,7 +26496,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.09</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -4414,7 +4414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5117,35 +5117,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -5206,35 +5206,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -5384,35 +5384,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -5473,35 +5473,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5651,35 +5651,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5740,35 +5740,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5847,7 +5847,7 @@
         <v>13730</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>15930</v>
+        <v>17010</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -5912,7 +5912,7 @@
         <v>15830</v>
       </c>
       <c r="T16" s="20" t="n">
-        <v>16200</v>
+        <v>17890</v>
       </c>
       <c r="U16" s="11" t="n"/>
       <c r="V16" s="10" t="n"/>
@@ -6042,7 +6042,7 @@
         <v>11494.2</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>14152.5</v>
+        <v>14708.2</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -8297,11 +8297,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>15930</v>
+        <v>17010</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,270원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,670원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26446,7 +26446,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.51</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="32">
@@ -26456,7 +26456,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.27</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="33">
@@ -26496,7 +26496,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16.13</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/452280_model.xlsx
+++ b/argus/kship/models/452280_model.xlsx
@@ -4414,7 +4414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5117,35 +5117,35 @@
         <v>1418.75</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="U6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AB6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AC6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE6" s="11" t="n"/>
     </row>
@@ -5206,35 +5206,35 @@
         <v>1355.4</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="U7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AB7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AC7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>890.41</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="U8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AB8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AC8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE8" s="11" t="n"/>
     </row>
@@ -5384,35 +5384,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="U9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Z9" s="11" t="n"/>
       <c r="AA9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AB9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AC9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="11" t="n"/>
     </row>
@@ -5473,35 +5473,35 @@
         <v>1631.97</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="W10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="X10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Z10" s="11" t="n"/>
       <c r="AA10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AB10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AC10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE10" s="11" t="n"/>
     </row>
@@ -5562,35 +5562,35 @@
         <v>1539.06</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="U11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="W11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="X11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AB11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AC11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="11" t="n"/>
     </row>
@@ -5651,35 +5651,35 @@
         <v>210.43</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="U12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="W12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AB12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AC12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE12" s="11" t="n"/>
     </row>
@@ -5740,35 +5740,35 @@
         <v>202.16</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="U13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="W13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="X13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AB13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AC13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="11" t="n"/>
     </row>
@@ -5847,7 +5847,7 @@
         <v>13730</v>
       </c>
       <c r="T15" s="20" t="n">
-        <v>17010</v>
+        <v>12750</v>
       </c>
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="10" t="n"/>
@@ -6042,7 +6042,7 @@
         <v>11494.2</v>
       </c>
       <c r="T18" s="20" t="n">
-        <v>14708.2</v>
+        <v>14792.5</v>
       </c>
       <c r="U18" s="11" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -8297,11 +8297,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>17010</v>
+        <v>12750</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,670원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,960원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -26446,7 +26446,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.7</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="32">
@@ -26456,7 +26456,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.49</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="33">
@@ -26496,7 +26496,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>17.12</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="37">
